--- a/12607922 (1).xlsx
+++ b/12607922 (1).xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -223,6 +223,18 @@
   </si>
   <si>
     <t>roam campus,chill day</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>homesick, chit chat with roommates</t>
   </si>
 </sst>
 </file>
@@ -1637,7 +1649,7 @@
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="7">
-        <v>46223</v>
+        <v>46254</v>
       </c>
       <c r="B6" s="8">
         <v>450</v>
@@ -1683,7 +1695,7 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="12">
-        <v>46224</v>
+        <v>46255</v>
       </c>
       <c r="B7" s="13">
         <v>450</v>
@@ -1729,7 +1741,7 @@
     </row>
     <row r="8" ht="29" spans="1:14">
       <c r="A8" s="12">
-        <v>46225</v>
+        <v>46256</v>
       </c>
       <c r="B8" s="13">
         <v>660</v>
@@ -1775,7 +1787,7 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="12">
-        <v>46226</v>
+        <v>46257</v>
       </c>
       <c r="B9" s="13">
         <v>660</v>
@@ -1819,27 +1831,51 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="12"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="14" t="str">
+    <row r="10" ht="29" spans="1:14">
+      <c r="A10" s="12">
+        <v>46258</v>
+      </c>
+      <c r="B10" s="13">
+        <v>360</v>
+      </c>
+      <c r="C10" s="13">
+        <v>30</v>
+      </c>
+      <c r="D10" s="13">
+        <v>60</v>
+      </c>
+      <c r="E10" s="13">
+        <v>30</v>
+      </c>
+      <c r="F10" s="13">
+        <v>150</v>
+      </c>
+      <c r="G10" s="13">
+        <v>3</v>
+      </c>
+      <c r="H10" s="13">
+        <v>240</v>
+      </c>
+      <c r="I10" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="14" t="str">
+        <v>870</v>
+      </c>
+      <c r="J10" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="16"/>
+        <v>570</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M10" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="N10" s="16" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="12"/>

--- a/12607922 (1).xlsx
+++ b/12607922 (1).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6200" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="6800" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -1878,21 +1878,25 @@
       </c>
     </row>
     <row r="11" spans="1:14">
-      <c r="A11" s="12"/>
-      <c r="B11" s="13"/>
+      <c r="A11" s="12">
+        <v>46259</v>
+      </c>
+      <c r="B11" s="13">
+        <v>360</v>
+      </c>
       <c r="C11" s="13"/>
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
       <c r="F11" s="13"/>
       <c r="G11" s="13"/>
       <c r="H11" s="13"/>
-      <c r="I11" s="14" t="str">
+      <c r="I11" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="14" t="str">
+        <v>360</v>
+      </c>
+      <c r="J11" s="14">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1080</v>
       </c>
       <c r="K11" s="15"/>
       <c r="L11" s="15"/>
@@ -1900,7 +1904,9 @@
       <c r="N11" s="16"/>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="12"/>
+      <c r="A12" s="12">
+        <v>46260</v>
+      </c>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
       <c r="D12" s="13"/>
@@ -1922,7 +1928,9 @@
       <c r="N12" s="16"/>
     </row>
     <row r="13" spans="1:14">
-      <c r="A13" s="12"/>
+      <c r="A13" s="12">
+        <v>46261</v>
+      </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
       <c r="D13" s="13"/>
@@ -1944,7 +1952,9 @@
       <c r="N13" s="16"/>
     </row>
     <row r="14" spans="1:14">
-      <c r="A14" s="12"/>
+      <c r="A14" s="12">
+        <v>46262</v>
+      </c>
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
       <c r="D14" s="13"/>
@@ -1966,7 +1976,9 @@
       <c r="N14" s="16"/>
     </row>
     <row r="15" spans="1:14">
-      <c r="A15" s="12"/>
+      <c r="A15" s="12">
+        <v>46263</v>
+      </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
       <c r="D15" s="13"/>

--- a/12607922 (1).xlsx
+++ b/12607922 (1).xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -235,6 +235,27 @@
   </si>
   <si>
     <t>homesick, chit chat with roommates</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>felt like doing nothing,tired from classes</t>
+  </si>
+  <si>
+    <t>roamed campus,made notes, less classes</t>
+  </si>
+  <si>
+    <t>went home,very tired,felt happy</t>
+  </si>
+  <si>
+    <t>very nice</t>
+  </si>
+  <si>
+    <t>spent rakhi with family</t>
+  </si>
+  <si>
+    <t>met old frienda,made notes,spent time with family</t>
   </si>
 </sst>
 </file>
@@ -1877,127 +1898,235 @@
         <v>68</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" ht="29" spans="1:14">
       <c r="A11" s="12">
         <v>46259</v>
       </c>
       <c r="B11" s="13">
-        <v>360</v>
-      </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
+        <v>420</v>
+      </c>
+      <c r="C11" s="13">
+        <v>100</v>
+      </c>
+      <c r="D11" s="13">
+        <v>0</v>
+      </c>
+      <c r="E11" s="13">
+        <v>0</v>
+      </c>
+      <c r="F11" s="13">
+        <v>420</v>
+      </c>
+      <c r="G11" s="13">
+        <v>7</v>
+      </c>
+      <c r="H11" s="13">
+        <v>120</v>
+      </c>
       <c r="I11" s="14">
         <f t="shared" si="0"/>
-        <v>360</v>
+        <v>1060</v>
       </c>
       <c r="J11" s="14">
         <f t="shared" si="1"/>
-        <v>1080</v>
-      </c>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="16"/>
-    </row>
-    <row r="12" spans="1:14">
+        <v>380</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M11" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="N11" s="16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" ht="29" spans="1:14">
       <c r="A12" s="12">
         <v>46260</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="14" t="str">
+      <c r="B12" s="13">
+        <v>480</v>
+      </c>
+      <c r="C12" s="13">
+        <v>100</v>
+      </c>
+      <c r="D12" s="13">
+        <v>120</v>
+      </c>
+      <c r="E12" s="13">
+        <v>60</v>
+      </c>
+      <c r="F12" s="13">
+        <v>240</v>
+      </c>
+      <c r="G12" s="13">
+        <v>4</v>
+      </c>
+      <c r="H12" s="13">
+        <v>180</v>
+      </c>
+      <c r="I12" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="14" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J12" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="16"/>
+        <v>260</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M12" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="N12" s="16" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="12">
         <v>46261</v>
       </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="14" t="str">
+      <c r="B13" s="13">
+        <v>480</v>
+      </c>
+      <c r="C13" s="13">
+        <v>100</v>
+      </c>
+      <c r="D13" s="13">
+        <v>0</v>
+      </c>
+      <c r="E13" s="13">
+        <v>0</v>
+      </c>
+      <c r="F13" s="13">
+        <v>300</v>
+      </c>
+      <c r="G13" s="13">
+        <v>6</v>
+      </c>
+      <c r="H13" s="13">
+        <v>300</v>
+      </c>
+      <c r="I13" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="14" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J13" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="16"/>
+        <v>260</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="L13" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M13" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="N13" s="16" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="12">
         <v>46262</v>
       </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="14" t="str">
+      <c r="B14" s="13">
+        <v>480</v>
+      </c>
+      <c r="C14" s="13">
+        <v>60</v>
+      </c>
+      <c r="D14" s="13">
+        <v>120</v>
+      </c>
+      <c r="E14" s="13">
+        <v>60</v>
+      </c>
+      <c r="F14" s="13">
+        <v>0</v>
+      </c>
+      <c r="G14" s="13">
+        <v>0</v>
+      </c>
+      <c r="H14" s="13">
+        <v>180</v>
+      </c>
+      <c r="I14" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="14" t="str">
+        <v>900</v>
+      </c>
+      <c r="J14" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="16"/>
-    </row>
-    <row r="15" spans="1:14">
+        <v>540</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="L14" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M14" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="N14" s="16" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" ht="29" spans="1:14">
       <c r="A15" s="12">
         <v>46263</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="14" t="str">
+      <c r="B15" s="13">
+        <v>600</v>
+      </c>
+      <c r="C15" s="13">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13">
+        <v>120</v>
+      </c>
+      <c r="E15" s="13">
+        <v>30</v>
+      </c>
+      <c r="F15" s="13">
+        <v>0</v>
+      </c>
+      <c r="G15" s="13">
+        <v>0</v>
+      </c>
+      <c r="H15" s="13">
+        <v>120</v>
+      </c>
+      <c r="I15" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="14" t="str">
+        <v>890</v>
+      </c>
+      <c r="J15" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="15"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="16"/>
+        <v>550</v>
+      </c>
+      <c r="K15" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="L15" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M15" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="N15" s="16" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="12"/>

--- a/12607922 (1).xlsx
+++ b/12607922 (1).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6800" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="6200" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -256,6 +256,27 @@
   </si>
   <si>
     <t>met old frienda,made notes,spent time with family</t>
+  </si>
+  <si>
+    <t>came back from home,stuck in jam for 2 hours,got tired , slept early</t>
+  </si>
+  <si>
+    <t>skipped classes,made notes for dbms and networking for ca,roamed campus with friends</t>
+  </si>
+  <si>
+    <t>very tired,didnt feel like doing much</t>
+  </si>
+  <si>
+    <t>completed notes</t>
+  </si>
+  <si>
+    <t>alot of classes,tired,missing family</t>
+  </si>
+  <si>
+    <t>came back home,celeberate janmashtmi</t>
+  </si>
+  <si>
+    <t>went to market,studied for ca,met friends at home</t>
   </si>
 </sst>
 </file>
@@ -2128,162 +2149,332 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="12"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="14" t="str">
+    <row r="16" ht="43.5" spans="1:14">
+      <c r="A16" s="12">
+        <v>46264</v>
+      </c>
+      <c r="B16" s="13">
+        <v>600</v>
+      </c>
+      <c r="C16" s="13">
+        <v>40</v>
+      </c>
+      <c r="D16" s="13">
+        <v>120</v>
+      </c>
+      <c r="E16" s="13">
+        <v>0</v>
+      </c>
+      <c r="F16" s="13">
+        <v>0</v>
+      </c>
+      <c r="G16" s="13">
+        <v>0</v>
+      </c>
+      <c r="H16" s="13">
+        <v>420</v>
+      </c>
+      <c r="I16" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="14" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J16" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="16"/>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" s="12"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="14" t="str">
+        <v>260</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="L16" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M16" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="N16" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" ht="43.5" spans="1:14">
+      <c r="A17" s="12">
+        <v>46265</v>
+      </c>
+      <c r="B17" s="13">
+        <v>600</v>
+      </c>
+      <c r="C17" s="13">
+        <v>40</v>
+      </c>
+      <c r="D17" s="13">
+        <v>300</v>
+      </c>
+      <c r="E17" s="13">
+        <v>60</v>
+      </c>
+      <c r="F17" s="13">
+        <v>180</v>
+      </c>
+      <c r="G17" s="13">
+        <v>0</v>
+      </c>
+      <c r="H17" s="13">
+        <v>180</v>
+      </c>
+      <c r="I17" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="14" t="str">
+        <v>1360</v>
+      </c>
+      <c r="J17" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="15"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="16"/>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" s="12"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="14" t="str">
+        <v>80</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="L17" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M17" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="N17" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" ht="29" spans="1:14">
+      <c r="A18" s="12">
+        <v>46266</v>
+      </c>
+      <c r="B18" s="13">
+        <v>450</v>
+      </c>
+      <c r="C18" s="13">
+        <v>30</v>
+      </c>
+      <c r="D18" s="13">
+        <v>30</v>
+      </c>
+      <c r="E18" s="13">
+        <v>20</v>
+      </c>
+      <c r="F18" s="13">
+        <v>420</v>
+      </c>
+      <c r="G18" s="13">
+        <v>7</v>
+      </c>
+      <c r="H18" s="13">
+        <v>180</v>
+      </c>
+      <c r="I18" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="14" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J18" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="15"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="16"/>
+        <v>310</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="L18" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M18" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="N18" s="16" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="19" spans="1:14">
-      <c r="A19" s="12"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="14" t="str">
+      <c r="A19" s="12">
+        <v>46267</v>
+      </c>
+      <c r="B19" s="13">
+        <v>440</v>
+      </c>
+      <c r="C19" s="13">
+        <v>40</v>
+      </c>
+      <c r="D19" s="13">
+        <v>120</v>
+      </c>
+      <c r="E19" s="13">
+        <v>30</v>
+      </c>
+      <c r="F19" s="13">
+        <v>240</v>
+      </c>
+      <c r="G19" s="13">
+        <v>4</v>
+      </c>
+      <c r="H19" s="13">
+        <v>240</v>
+      </c>
+      <c r="I19" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="14" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J19" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="15"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="16"/>
-    </row>
-    <row r="20" spans="1:14">
-      <c r="A20" s="12"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="14" t="str">
+        <v>330</v>
+      </c>
+      <c r="K19" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L19" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M19" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="N19" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" ht="29" spans="1:14">
+      <c r="A20" s="12">
+        <v>46268</v>
+      </c>
+      <c r="B20" s="13">
+        <v>420</v>
+      </c>
+      <c r="C20" s="13">
+        <v>40</v>
+      </c>
+      <c r="D20" s="13">
+        <v>80</v>
+      </c>
+      <c r="E20" s="13">
+        <v>30</v>
+      </c>
+      <c r="F20" s="13">
+        <v>420</v>
+      </c>
+      <c r="G20" s="13">
+        <v>7</v>
+      </c>
+      <c r="H20" s="13">
+        <v>120</v>
+      </c>
+      <c r="I20" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="14" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J20" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="15"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="16"/>
-    </row>
-    <row r="21" spans="1:14">
-      <c r="A21" s="12"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="14" t="str">
+        <v>330</v>
+      </c>
+      <c r="K20" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="L20" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M20" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="N20" s="16" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" ht="29" spans="1:14">
+      <c r="A21" s="12">
+        <v>46269</v>
+      </c>
+      <c r="B21" s="13">
+        <v>480</v>
+      </c>
+      <c r="C21" s="13">
+        <v>30</v>
+      </c>
+      <c r="D21" s="13">
+        <v>0</v>
+      </c>
+      <c r="E21" s="13">
+        <v>0</v>
+      </c>
+      <c r="F21" s="13">
+        <v>360</v>
+      </c>
+      <c r="G21" s="13">
+        <v>6</v>
+      </c>
+      <c r="H21" s="13">
+        <v>200</v>
+      </c>
+      <c r="I21" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="14" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J21" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="15"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="15"/>
-      <c r="N21" s="16"/>
-    </row>
-    <row r="22" spans="1:14">
-      <c r="A22" s="12"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="14" t="str">
+        <v>370</v>
+      </c>
+      <c r="K21" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L21" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M21" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="N21" s="16" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" ht="29" spans="1:14">
+      <c r="A22" s="12">
+        <v>46270</v>
+      </c>
+      <c r="B22" s="13">
+        <v>600</v>
+      </c>
+      <c r="C22" s="13">
+        <v>30</v>
+      </c>
+      <c r="D22" s="13">
+        <v>120</v>
+      </c>
+      <c r="E22" s="13">
+        <v>30</v>
+      </c>
+      <c r="F22" s="13">
+        <v>0</v>
+      </c>
+      <c r="G22" s="13">
+        <v>0</v>
+      </c>
+      <c r="H22" s="13">
+        <v>300</v>
+      </c>
+      <c r="I22" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="14" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J22" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="15"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="16"/>
+        <v>360</v>
+      </c>
+      <c r="K22" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="L22" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M22" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="N22" s="16" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="23" spans="1:14">
-      <c r="A23" s="12"/>
+      <c r="A23" s="12">
+        <v>46271</v>
+      </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
       <c r="D23" s="13"/>
@@ -2305,7 +2496,9 @@
       <c r="N23" s="16"/>
     </row>
     <row r="24" spans="1:14">
-      <c r="A24" s="12"/>
+      <c r="A24" s="12">
+        <v>46272</v>
+      </c>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
       <c r="D24" s="13"/>
@@ -2327,7 +2520,9 @@
       <c r="N24" s="16"/>
     </row>
     <row r="25" spans="1:14">
-      <c r="A25" s="12"/>
+      <c r="A25" s="12">
+        <v>46273</v>
+      </c>
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
       <c r="D25" s="13"/>
@@ -2349,7 +2544,9 @@
       <c r="N25" s="16"/>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26" s="12"/>
+      <c r="A26" s="12">
+        <v>46274</v>
+      </c>
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
       <c r="D26" s="13"/>
@@ -2371,7 +2568,9 @@
       <c r="N26" s="16"/>
     </row>
     <row r="27" spans="1:14">
-      <c r="A27" s="12"/>
+      <c r="A27" s="12">
+        <v>46275</v>
+      </c>
       <c r="B27" s="13"/>
       <c r="C27" s="13"/>
       <c r="D27" s="13"/>
@@ -2393,7 +2592,9 @@
       <c r="N27" s="16"/>
     </row>
     <row r="28" spans="1:14">
-      <c r="A28" s="12"/>
+      <c r="A28" s="12">
+        <v>46276</v>
+      </c>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
@@ -2415,7 +2616,9 @@
       <c r="N28" s="16"/>
     </row>
     <row r="29" spans="1:14">
-      <c r="A29" s="12"/>
+      <c r="A29" s="12">
+        <v>46277</v>
+      </c>
       <c r="B29" s="13"/>
       <c r="C29" s="13"/>
       <c r="D29" s="13"/>
@@ -2437,7 +2640,9 @@
       <c r="N29" s="16"/>
     </row>
     <row r="30" spans="1:14">
-      <c r="A30" s="12"/>
+      <c r="A30" s="12">
+        <v>46278</v>
+      </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
       <c r="D30" s="13"/>
@@ -2459,7 +2664,9 @@
       <c r="N30" s="16"/>
     </row>
     <row r="31" spans="1:14">
-      <c r="A31" s="12"/>
+      <c r="A31" s="12">
+        <v>46279</v>
+      </c>
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
       <c r="D31" s="13"/>
@@ -2481,7 +2688,9 @@
       <c r="N31" s="16"/>
     </row>
     <row r="32" spans="1:14">
-      <c r="A32" s="12"/>
+      <c r="A32" s="12">
+        <v>46280</v>
+      </c>
       <c r="B32" s="13"/>
       <c r="C32" s="13"/>
       <c r="D32" s="13"/>
@@ -2503,7 +2712,9 @@
       <c r="N32" s="16"/>
     </row>
     <row r="33" spans="1:14">
-      <c r="A33" s="12"/>
+      <c r="A33" s="12">
+        <v>46281</v>
+      </c>
       <c r="B33" s="13"/>
       <c r="C33" s="13"/>
       <c r="D33" s="13"/>
@@ -2525,7 +2736,9 @@
       <c r="N33" s="16"/>
     </row>
     <row r="34" spans="1:14">
-      <c r="A34" s="12"/>
+      <c r="A34" s="12">
+        <v>46282</v>
+      </c>
       <c r="B34" s="13"/>
       <c r="C34" s="13"/>
       <c r="D34" s="13"/>
@@ -2547,7 +2760,9 @@
       <c r="N34" s="16"/>
     </row>
     <row r="35" spans="1:14">
-      <c r="A35" s="12"/>
+      <c r="A35" s="12">
+        <v>46283</v>
+      </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
       <c r="D35" s="13"/>
@@ -2569,7 +2784,9 @@
       <c r="N35" s="16"/>
     </row>
     <row r="36" spans="1:14">
-      <c r="A36" s="12"/>
+      <c r="A36" s="12">
+        <v>46284</v>
+      </c>
       <c r="B36" s="13"/>
       <c r="C36" s="13"/>
       <c r="D36" s="13"/>
@@ -2591,7 +2808,9 @@
       <c r="N36" s="16"/>
     </row>
     <row r="37" spans="1:14">
-      <c r="A37" s="12"/>
+      <c r="A37" s="12">
+        <v>46285</v>
+      </c>
       <c r="B37" s="13"/>
       <c r="C37" s="13"/>
       <c r="D37" s="13"/>
@@ -2613,7 +2832,9 @@
       <c r="N37" s="16"/>
     </row>
     <row r="38" spans="1:14">
-      <c r="A38" s="12"/>
+      <c r="A38" s="12">
+        <v>46286</v>
+      </c>
       <c r="B38" s="13"/>
       <c r="C38" s="13"/>
       <c r="D38" s="13"/>
@@ -2635,7 +2856,9 @@
       <c r="N38" s="16"/>
     </row>
     <row r="39" spans="1:14">
-      <c r="A39" s="12"/>
+      <c r="A39" s="12">
+        <v>46287</v>
+      </c>
       <c r="B39" s="13"/>
       <c r="C39" s="13"/>
       <c r="D39" s="13"/>
@@ -2657,7 +2880,9 @@
       <c r="N39" s="16"/>
     </row>
     <row r="40" spans="1:14">
-      <c r="A40" s="12"/>
+      <c r="A40" s="12">
+        <v>46288</v>
+      </c>
       <c r="B40" s="13"/>
       <c r="C40" s="13"/>
       <c r="D40" s="13"/>
@@ -2679,7 +2904,9 @@
       <c r="N40" s="16"/>
     </row>
     <row r="41" spans="1:14">
-      <c r="A41" s="12"/>
+      <c r="A41" s="12">
+        <v>46289</v>
+      </c>
       <c r="B41" s="13"/>
       <c r="C41" s="13"/>
       <c r="D41" s="13"/>
@@ -2701,7 +2928,9 @@
       <c r="N41" s="16"/>
     </row>
     <row r="42" spans="1:14">
-      <c r="A42" s="12"/>
+      <c r="A42" s="12">
+        <v>46290</v>
+      </c>
       <c r="B42" s="13"/>
       <c r="C42" s="13"/>
       <c r="D42" s="13"/>
@@ -2723,7 +2952,9 @@
       <c r="N42" s="16"/>
     </row>
     <row r="43" spans="1:14">
-      <c r="A43" s="12"/>
+      <c r="A43" s="12">
+        <v>46291</v>
+      </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
       <c r="D43" s="13"/>
@@ -2745,7 +2976,9 @@
       <c r="N43" s="16"/>
     </row>
     <row r="44" spans="1:14">
-      <c r="A44" s="12"/>
+      <c r="A44" s="12">
+        <v>46292</v>
+      </c>
       <c r="B44" s="13"/>
       <c r="C44" s="13"/>
       <c r="D44" s="13"/>
@@ -2767,7 +3000,9 @@
       <c r="N44" s="16"/>
     </row>
     <row r="45" spans="1:14">
-      <c r="A45" s="12"/>
+      <c r="A45" s="12">
+        <v>46293</v>
+      </c>
       <c r="B45" s="13"/>
       <c r="C45" s="13"/>
       <c r="D45" s="13"/>
@@ -2789,7 +3024,9 @@
       <c r="N45" s="16"/>
     </row>
     <row r="46" spans="1:14">
-      <c r="A46" s="12"/>
+      <c r="A46" s="12">
+        <v>46294</v>
+      </c>
       <c r="B46" s="13"/>
       <c r="C46" s="13"/>
       <c r="D46" s="13"/>
@@ -2811,7 +3048,9 @@
       <c r="N46" s="16"/>
     </row>
     <row r="47" spans="1:14">
-      <c r="A47" s="12"/>
+      <c r="A47" s="12">
+        <v>46295</v>
+      </c>
       <c r="B47" s="13"/>
       <c r="C47" s="13"/>
       <c r="D47" s="13"/>
